--- a/data/cox_xlsx/ISS.CO.xlsx
+++ b/data/cox_xlsx/ISS.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="397">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -762,28 +762,31 @@
     <t>Total Equity</t>
   </si>
   <si>
+    <t>Loans and borrowings LT</t>
+  </si>
+  <si>
+    <t>Pensions and similar obligations</t>
+  </si>
+  <si>
+    <t>Deferred tax liabilities</t>
+  </si>
+  <si>
+    <t>Provisions</t>
+  </si>
+  <si>
+    <t>Legal and labour related cases</t>
+  </si>
+  <si>
+    <t>Provisions - Restructuring - Long-Term</t>
+  </si>
+  <si>
+    <t>Provisions - Balancing value</t>
+  </si>
+  <si>
+    <t>Non-current liabilities</t>
+  </si>
+  <si>
     <t>Loans and borrowings</t>
-  </si>
-  <si>
-    <t>Pensions and similar obligations</t>
-  </si>
-  <si>
-    <t>Deferred tax liabilities</t>
-  </si>
-  <si>
-    <t>Provisions</t>
-  </si>
-  <si>
-    <t>Legal and labour related cases</t>
-  </si>
-  <si>
-    <t>Provisions - Restructuring - Long-Term</t>
-  </si>
-  <si>
-    <t>Provisions - Balancing value</t>
-  </si>
-  <si>
-    <t>Non-current liabilities</t>
   </si>
   <si>
     <t>Bank loans and overdrafts</t>
@@ -1332,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1416,6 +1419,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -10011,11 +10017,20 @@
       <c r="A31" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="B31" s="15">
+        <f t="shared" ref="B31:E31" si="1">B36+B39</f>
+        <v>5297.77</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" si="1"/>
+        <v>5400.21</v>
+      </c>
+      <c r="D31" s="15">
+        <f t="shared" si="1"/>
+        <v>4690.76</v>
+      </c>
       <c r="E31" s="15">
-        <f>E36+E39</f>
+        <f t="shared" si="1"/>
         <v>4681.99</v>
       </c>
       <c r="F31" s="18">
@@ -12171,7 +12186,7 @@
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="28" t="s">
         <v>247</v>
       </c>
       <c r="B79" s="15">
@@ -12566,7 +12581,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B87" s="18">
         <v>8407.78</v>
@@ -12622,7 +12637,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B88" s="18">
         <v>604.28</v>
@@ -12660,7 +12675,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B89" s="18">
         <v>7803.49</v>
@@ -12698,7 +12713,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B90" s="15">
         <v>11002.08</v>
@@ -12754,7 +12769,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B91" s="18">
         <v>678.63</v>
@@ -12810,7 +12825,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B92" s="15">
         <v>15399.75</v>
@@ -12866,7 +12881,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -12918,7 +12933,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B94" s="18">
         <v>1860.31</v>
@@ -13002,7 +13017,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -13026,7 +13041,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B97" s="18">
         <v>3024.58</v>
@@ -13062,7 +13077,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="15">
         <v>10470.57</v>
@@ -13174,7 +13189,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15">
@@ -13228,7 +13243,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B101" s="17">
         <v>35973.89</v>
@@ -13284,7 +13299,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B102" s="17">
         <v>55462.84</v>
@@ -13340,7 +13355,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B103" s="17">
         <v>72136.02</v>
@@ -13396,7 +13411,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B104" s="18">
         <v>161.43</v>
@@ -13452,7 +13467,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B105" s="18">
         <v>174.2</v>
@@ -13508,7 +13523,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B106" s="19">
         <v>12.77</v>
@@ -13564,7 +13579,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B107" s="18">
         <v>6974.58</v>
@@ -13602,7 +13617,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B108" s="18">
         <v>7452.31</v>
@@ -13640,7 +13655,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B109" s="18">
         <v>235.7</v>
@@ -13678,7 +13693,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B110" s="18">
         <v>6009.62</v>
@@ -13716,7 +13731,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B111" s="15">
         <v>0.0</v>
@@ -13754,7 +13769,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B112" s="15">
         <v>0.0</v>
@@ -13792,7 +13807,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B113" s="15"/>
       <c r="C113" s="15">
@@ -13828,7 +13843,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B114" s="18">
         <v>1551.84</v>
@@ -13870,7 +13885,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B115" s="18">
         <v>990.27</v>
@@ -13908,7 +13923,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B116" s="18">
         <v>675.47</v>
@@ -13946,7 +13961,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B117" s="18">
         <v>431.86</v>
@@ -13984,7 +13999,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B118" s="18">
         <v>153.44</v>
@@ -14026,7 +14041,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B119" s="18">
         <v>327.45</v>
@@ -14068,7 +14083,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B120" s="18">
         <v>4130.33</v>
@@ -14112,7 +14127,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -14138,7 +14153,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B122" s="15">
         <v>10627.18</v>
@@ -14172,7 +14187,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -14202,7 +14217,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B124" s="18">
         <v>174.2</v>
@@ -14258,7 +14273,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B125" s="19">
         <v>12.77</v>
@@ -14314,7 +14329,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B126" s="18">
         <v>161.43</v>
@@ -14370,7 +14385,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B127" s="19">
         <v>1.0</v>
@@ -14426,7 +14441,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B128" s="15">
         <v>256006.0</v>
@@ -14482,7 +14497,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B129" s="15">
         <v>70522.0</v>
@@ -14508,7 +14523,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -14550,7 +14565,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -14592,7 +14607,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -14634,7 +14649,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -14676,7 +14691,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -14718,7 +14733,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -14760,7 +14775,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -15686,7 +15701,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16007,55 +16022,55 @@
         <v>39</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -16116,7 +16131,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -16194,7 +16209,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B20" s="18">
         <v>6538.32</v>
@@ -16250,7 +16265,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B21" s="15">
         <v>0.0</v>
@@ -16346,7 +16361,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B23" s="18">
         <v>145.85</v>
@@ -16392,7 +16407,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B24" s="21">
         <v>-839.05</v>
@@ -16448,7 +16463,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B25" s="19">
         <v>3.14</v>
@@ -16502,7 +16517,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B26" s="21">
         <v>-1193.49</v>
@@ -16556,7 +16571,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B27" s="18">
         <v>351.3</v>
@@ -16610,7 +16625,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -16634,7 +16649,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B29" s="21">
         <v>-103.51</v>
@@ -16690,7 +16705,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B30" s="20">
         <v>-72.14</v>
@@ -16722,7 +16737,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -16768,7 +16783,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" s="18">
         <v>265.05</v>
@@ -16814,7 +16829,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B33" s="21">
         <v>-1105.66</v>
@@ -16860,7 +16875,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B34" s="21">
         <v>-917.47</v>
@@ -16916,7 +16931,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -16940,7 +16955,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B36" s="20">
         <v>-94.1</v>
@@ -16970,7 +16985,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B37" s="22">
         <v>6256.02</v>
@@ -17026,7 +17041,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" s="21">
         <v>-534.8</v>
@@ -17082,7 +17097,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B39" s="21">
         <v>-141.15</v>
@@ -17138,7 +17153,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" s="21">
         <v>-1046.07</v>
@@ -17194,7 +17209,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B41" s="19">
         <v>25.09</v>
@@ -17250,7 +17265,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B42" s="18">
         <v>133.31</v>
@@ -17306,7 +17321,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" s="21">
         <v>-293.28</v>
@@ -17330,7 +17345,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" s="23">
         <v>-1856.89</v>
@@ -17386,7 +17401,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17434,7 +17449,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" s="21">
         <v>-5852.96</v>
@@ -17488,7 +17503,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" s="21">
         <v>-4406.98</v>
@@ -17520,7 +17535,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -17552,7 +17567,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17584,7 +17599,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -17614,7 +17629,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B51" s="15">
         <v>0.0</v>
@@ -17640,7 +17655,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15">
@@ -17674,7 +17689,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B53" s="21">
         <v>-837.48</v>
@@ -17716,7 +17731,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -17762,7 +17777,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" s="21">
         <v>-112.92</v>
@@ -17804,7 +17819,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B56" s="21">
         <v>-1400.51</v>
@@ -17840,7 +17855,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B57" s="18">
         <v>632.03</v>
@@ -17864,9 +17879,9 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="B58" s="28">
+        <v>340</v>
+      </c>
+      <c r="B58" s="29">
         <v>-11978.82</v>
       </c>
       <c r="C58" s="23">
@@ -17920,7 +17935,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B59" s="15">
         <v>10802.77</v>
@@ -17976,7 +17991,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B60" s="18">
         <v>2735.1</v>
@@ -18032,7 +18047,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B61" s="21">
         <v>-418.74</v>
@@ -18088,7 +18103,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B62" s="21">
         <v>-7579.68</v>
@@ -18140,7 +18155,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B63" s="23">
         <v>-7998.42</v>
@@ -18196,7 +18211,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B64" s="18">
         <v>4160.75</v>
@@ -19190,7 +19205,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19620,7 +19635,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19697,1766 +19712,1766 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
+      <c r="A20" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="B21" s="32">
+      <c r="A21" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" s="33">
         <v>82202.01</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>57908.29</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>52815.18</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>55989.17</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>49777.65</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>49982.04</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>58687.02</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>59231.63</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>74107.96</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>67629.85</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>73758.5</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>55536.49</v>
       </c>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="B22" s="33">
         <v>63442.51</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>58093.19</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>57593.06</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>56789.96</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>58617.71</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>66459.37</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>67952.89</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>68745.91</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
+      <c r="A23" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="B24" s="33">
         <v>59852.98</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>38470.99</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>35926.35</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>38568.5</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>31249.99</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>27553.12</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>39107.58</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>44848.61</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>59019.7</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>54121.32</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>59399.84</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>40145.0</v>
       </c>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="B25" s="32">
+      <c r="A25" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B25" s="33">
         <v>43253.41</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>37383.95</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>37138.29</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>37683.49</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>40629.98</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>48414.02</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>52321.22</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>53584.3</v>
       </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
+      <c r="A26" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B27" s="34">
         <v>343.59</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>207.2</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>193.5</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>207.73</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>168.31</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>148.4</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>210.63</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>241.55</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>317.88</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>291.49</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>319.92</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>216.22</v>
       </c>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="B28" s="34">
         <v>237.21</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>201.35</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>200.02</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>202.96</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>218.83</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>260.76</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>281.8</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>288.6</v>
       </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="B30" s="35">
         <v>9.06</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>13.01</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>11.66</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>9.1</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>10.99</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>-5.87</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>2.83</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>6.39</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>5.26</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>6.38</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>6.06</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>4.94</v>
       </c>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="35">
         <v>10.53</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>8.32</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>6.08</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>5.16</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>4.47</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>4.08</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>5.53</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>5.83</v>
       </c>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="B33" s="34">
+      <c r="A33" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" s="35">
         <v>1.43</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>1.75</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>1.63</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>0.0</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>0.0</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>0.0</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>4.82</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>4.23</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>3.2</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>4.78</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>1.97</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>0.0</v>
       </c>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" s="35">
         <v>1.0</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>0.69</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>1.47</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>2.14</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>2.84</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>3.73</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>3.68</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="35">
         <v>2.91</v>
       </c>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="B35" s="34">
+      <c r="A35" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" s="35">
         <v>1.43</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>1.75</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>1.63</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>0.0</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>0.0</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>0.0</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>4.82</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>4.23</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>3.2</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>4.78</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>1.97</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>0.0</v>
       </c>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" s="35">
         <v>1.0</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>0.69</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>1.47</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>2.14</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>2.84</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>3.73</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>3.68</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>2.91</v>
       </c>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
+      <c r="A37" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="B38" s="36">
+      <c r="A38" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="B38" s="37">
         <v>3.59</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="37">
         <v>2.08</v>
       </c>
-      <c r="D38" s="36">
+      <c r="D38" s="37">
         <v>2.42</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="37">
         <v>2.68</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F38" s="37">
         <v>3.04</v>
       </c>
-      <c r="G38" s="36">
+      <c r="G38" s="37">
         <v>2.99</v>
       </c>
-      <c r="H38" s="36">
+      <c r="H38" s="37">
         <v>2.36</v>
       </c>
-      <c r="I38" s="36">
+      <c r="I38" s="37">
         <v>2.7</v>
       </c>
-      <c r="J38" s="36">
+      <c r="J38" s="37">
         <v>3.21</v>
       </c>
-      <c r="K38" s="36">
+      <c r="K38" s="37">
         <v>3.15</v>
       </c>
-      <c r="L38" s="36">
+      <c r="L38" s="37">
         <v>3.16</v>
       </c>
-      <c r="M38" s="36">
+      <c r="M38" s="37">
         <v>2.55</v>
       </c>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32"/>
-      <c r="R38" s="32"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="B39" s="36">
+      <c r="A39" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="B39" s="37">
         <v>2.75</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="37">
         <v>2.57</v>
       </c>
-      <c r="D39" s="36">
+      <c r="D39" s="37">
         <v>2.64</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="37">
         <v>2.7</v>
       </c>
-      <c r="F39" s="36">
+      <c r="F39" s="37">
         <v>2.84</v>
       </c>
-      <c r="G39" s="36">
+      <c r="G39" s="37">
         <v>2.88</v>
       </c>
-      <c r="H39" s="36">
+      <c r="H39" s="37">
         <v>2.93</v>
       </c>
-      <c r="I39" s="36">
+      <c r="I39" s="37">
         <v>2.96</v>
       </c>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
+      <c r="A40" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="B41" s="36">
+      <c r="A41" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" s="37">
         <v>0.43</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="37">
         <v>0.29</v>
       </c>
-      <c r="D41" s="36">
+      <c r="D41" s="37">
         <v>0.31</v>
       </c>
-      <c r="E41" s="36">
+      <c r="E41" s="37">
         <v>0.37</v>
       </c>
-      <c r="F41" s="36">
+      <c r="F41" s="37">
         <v>0.33</v>
       </c>
-      <c r="G41" s="36">
+      <c r="G41" s="37">
         <v>0.28</v>
       </c>
-      <c r="H41" s="36">
+      <c r="H41" s="37">
         <v>0.38</v>
       </c>
-      <c r="I41" s="36">
+      <c r="I41" s="37">
         <v>0.46</v>
       </c>
-      <c r="J41" s="36">
+      <c r="J41" s="37">
         <v>0.61</v>
       </c>
-      <c r="K41" s="36">
+      <c r="K41" s="37">
         <v>0.56</v>
       </c>
-      <c r="L41" s="36">
+      <c r="L41" s="37">
         <v>0.58</v>
       </c>
-      <c r="M41" s="36">
+      <c r="M41" s="37">
         <v>0.42</v>
       </c>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="32"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="B42" s="36">
+      <c r="A42" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="B42" s="37">
         <v>0.35</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="37">
         <v>0.31</v>
       </c>
-      <c r="D42" s="36">
+      <c r="D42" s="37">
         <v>0.33</v>
       </c>
-      <c r="E42" s="36">
+      <c r="E42" s="37">
         <v>0.36</v>
       </c>
-      <c r="F42" s="36">
+      <c r="F42" s="37">
         <v>0.41</v>
       </c>
-      <c r="G42" s="36">
+      <c r="G42" s="37">
         <v>0.46</v>
       </c>
-      <c r="H42" s="36">
+      <c r="H42" s="37">
         <v>0.52</v>
       </c>
-      <c r="I42" s="36">
+      <c r="I42" s="37">
         <v>0.53</v>
       </c>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
+      <c r="A43" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="B44" s="36">
+      <c r="A44" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="B44" s="37">
         <v>11.04</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="37">
         <v>7.69</v>
       </c>
-      <c r="D44" s="36">
+      <c r="D44" s="37">
         <v>8.57</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="37">
         <v>10.98</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="37">
         <v>9.1</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="36">
+      <c r="G44" s="33"/>
+      <c r="H44" s="37">
         <v>35.31</v>
       </c>
-      <c r="I44" s="36">
+      <c r="I44" s="37">
         <v>15.66</v>
       </c>
-      <c r="J44" s="36">
+      <c r="J44" s="37">
         <v>19.0</v>
       </c>
-      <c r="K44" s="36">
+      <c r="K44" s="37">
         <v>15.67</v>
       </c>
-      <c r="L44" s="36">
+      <c r="L44" s="37">
         <v>16.49</v>
       </c>
-      <c r="M44" s="36">
+      <c r="M44" s="37">
         <v>20.24</v>
       </c>
-      <c r="N44" s="32"/>
-      <c r="O44" s="32"/>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="32"/>
-      <c r="R44" s="32"/>
+      <c r="N44" s="33"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="B45" s="36">
+      <c r="A45" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="B45" s="37">
         <v>9.5</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="37">
         <v>12.02</v>
       </c>
-      <c r="D45" s="36">
+      <c r="D45" s="37">
         <v>16.44</v>
       </c>
-      <c r="E45" s="36">
+      <c r="E45" s="37">
         <v>19.39</v>
       </c>
-      <c r="F45" s="36">
+      <c r="F45" s="37">
         <v>22.35</v>
       </c>
-      <c r="G45" s="36">
+      <c r="G45" s="37">
         <v>24.48</v>
       </c>
-      <c r="H45" s="36">
+      <c r="H45" s="37">
         <v>18.1</v>
       </c>
-      <c r="I45" s="36">
+      <c r="I45" s="37">
         <v>17.16</v>
       </c>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="32"/>
-      <c r="O45" s="32"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="32"/>
-      <c r="R45" s="32"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>372</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
+      <c r="A46" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="B47" s="36">
+      <c r="A47" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="B47" s="37">
         <v>8.6</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="37">
         <v>5.73</v>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="37">
         <v>6.91</v>
       </c>
-      <c r="E47" s="36">
+      <c r="E47" s="37">
         <v>7.55</v>
       </c>
-      <c r="F47" s="36">
+      <c r="F47" s="37">
         <v>10.41</v>
       </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="36">
+      <c r="G47" s="33"/>
+      <c r="H47" s="37">
         <v>9.5</v>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="37">
         <v>9.85</v>
       </c>
-      <c r="J47" s="36">
+      <c r="J47" s="37">
         <v>12.11</v>
       </c>
-      <c r="K47" s="36">
+      <c r="K47" s="37">
         <v>10.5</v>
       </c>
-      <c r="L47" s="36">
+      <c r="L47" s="37">
         <v>11.04</v>
       </c>
-      <c r="M47" s="36">
+      <c r="M47" s="37">
         <v>9.99</v>
       </c>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="B48" s="36">
+      <c r="A48" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="B48" s="37">
         <v>7.62</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="37">
         <v>11.66</v>
       </c>
-      <c r="D48" s="36">
+      <c r="D48" s="37">
         <v>13.7</v>
       </c>
-      <c r="E48" s="36">
+      <c r="E48" s="37">
         <v>14.85</v>
       </c>
-      <c r="F48" s="36">
+      <c r="F48" s="37">
         <v>16.66</v>
       </c>
-      <c r="G48" s="36">
+      <c r="G48" s="37">
         <v>15.58</v>
       </c>
-      <c r="H48" s="36">
+      <c r="H48" s="37">
         <v>10.65</v>
       </c>
-      <c r="I48" s="36">
+      <c r="I48" s="37">
         <v>10.73</v>
       </c>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
-      <c r="N48" s="32"/>
-      <c r="O48" s="32"/>
-      <c r="P48" s="32"/>
-      <c r="Q48" s="32"/>
-      <c r="R48" s="32"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
+      <c r="A49" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="B50" s="36">
+      <c r="A50" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" s="37">
         <v>14.09</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="37">
         <v>9.12</v>
       </c>
-      <c r="D50" s="36">
+      <c r="D50" s="37">
         <v>12.55</v>
       </c>
-      <c r="E50" s="36">
+      <c r="E50" s="37">
         <v>13.54</v>
       </c>
-      <c r="F50" s="36">
+      <c r="F50" s="37">
         <v>45.23</v>
       </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="36">
+      <c r="G50" s="33"/>
+      <c r="H50" s="37">
         <v>17.2</v>
       </c>
-      <c r="I50" s="36">
+      <c r="I50" s="37">
         <v>14.86</v>
       </c>
-      <c r="J50" s="36">
+      <c r="J50" s="37">
         <v>18.26</v>
       </c>
-      <c r="K50" s="36">
+      <c r="K50" s="37">
         <v>15.31</v>
       </c>
-      <c r="L50" s="36">
+      <c r="L50" s="37">
         <v>16.58</v>
       </c>
-      <c r="M50" s="36">
+      <c r="M50" s="37">
         <v>17.27</v>
       </c>
-      <c r="N50" s="32"/>
-      <c r="O50" s="32"/>
-      <c r="P50" s="32"/>
-      <c r="Q50" s="32"/>
-      <c r="R50" s="32"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="B51" s="36">
+      <c r="A51" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="B51" s="37">
         <v>13.95</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="37">
         <v>63.8</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>136.15</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>104.75</v>
       </c>
-      <c r="F51" s="36">
+      <c r="F51" s="37">
         <v>88.78</v>
       </c>
-      <c r="G51" s="36">
+      <c r="G51" s="37">
         <v>42.16</v>
       </c>
-      <c r="H51" s="36">
+      <c r="H51" s="37">
         <v>16.38</v>
       </c>
-      <c r="I51" s="36">
+      <c r="I51" s="37">
         <v>16.41</v>
       </c>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-      <c r="N51" s="32"/>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="32"/>
-      <c r="R51" s="32"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
+      <c r="A52" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="B53" s="36">
+      <c r="A53" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="B53" s="37">
         <v>14.16</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="37">
         <v>9.18</v>
       </c>
-      <c r="D53" s="36">
+      <c r="D53" s="37">
         <v>7.73</v>
       </c>
-      <c r="E53" s="36">
+      <c r="E53" s="37">
         <v>14.7</v>
       </c>
-      <c r="F53" s="36">
+      <c r="F53" s="37">
         <v>39.74</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="36">
+      <c r="G53" s="33"/>
+      <c r="H53" s="37">
         <v>18.05</v>
       </c>
-      <c r="I53" s="36">
+      <c r="I53" s="37">
         <v>11.17</v>
       </c>
-      <c r="J53" s="36">
+      <c r="J53" s="37">
         <v>14.93</v>
       </c>
-      <c r="K53" s="36">
+      <c r="K53" s="37">
         <v>13.79</v>
       </c>
-      <c r="L53" s="36">
+      <c r="L53" s="37">
         <v>17.26</v>
       </c>
-      <c r="M53" s="36">
+      <c r="M53" s="37">
         <v>15.62</v>
       </c>
-      <c r="N53" s="32"/>
-      <c r="O53" s="32"/>
-      <c r="P53" s="32"/>
-      <c r="Q53" s="32"/>
-      <c r="R53" s="32"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="B54" s="36">
+      <c r="A54" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="B54" s="37">
         <v>2.75</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="37">
         <v>2.57</v>
       </c>
-      <c r="D54" s="36">
+      <c r="D54" s="37">
         <v>2.64</v>
       </c>
-      <c r="E54" s="36">
+      <c r="E54" s="37">
         <v>2.7</v>
       </c>
-      <c r="F54" s="36">
+      <c r="F54" s="37">
         <v>2.84</v>
       </c>
-      <c r="G54" s="36">
+      <c r="G54" s="37">
         <v>2.88</v>
       </c>
-      <c r="H54" s="36">
+      <c r="H54" s="37">
         <v>2.93</v>
       </c>
-      <c r="I54" s="36">
+      <c r="I54" s="37">
         <v>2.96</v>
       </c>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
-      <c r="N54" s="32"/>
-      <c r="O54" s="32"/>
-      <c r="P54" s="32"/>
-      <c r="Q54" s="32"/>
-      <c r="R54" s="32"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="33"/>
+      <c r="R54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
+      <c r="A55" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="B56" s="36">
+      <c r="A56" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="B56" s="37">
         <v>2.0</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="37">
         <v>0.23</v>
       </c>
-      <c r="D56" s="37">
+      <c r="D56" s="38">
         <v>-2.26</v>
       </c>
-      <c r="E56" s="36">
+      <c r="E56" s="37">
         <v>0.05</v>
       </c>
-      <c r="F56" s="36">
+      <c r="F56" s="37">
         <v>0.41</v>
       </c>
-      <c r="G56" s="32"/>
-      <c r="H56" s="37">
+      <c r="G56" s="33"/>
+      <c r="H56" s="38">
         <v>-0.71</v>
       </c>
-      <c r="I56" s="37">
+      <c r="I56" s="38">
         <v>-2.14</v>
       </c>
-      <c r="J56" s="37">
+      <c r="J56" s="38">
         <v>-1.18</v>
       </c>
-      <c r="K56" s="36">
+      <c r="K56" s="37">
         <v>4.01</v>
       </c>
-      <c r="L56" s="36">
+      <c r="L56" s="37">
         <v>0.36</v>
       </c>
-      <c r="M56" s="36">
+      <c r="M56" s="37">
         <v>0.47</v>
       </c>
-      <c r="N56" s="32"/>
-      <c r="O56" s="32"/>
-      <c r="P56" s="32"/>
-      <c r="Q56" s="32"/>
-      <c r="R56" s="32"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="36">
+      <c r="A57" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="B57" s="33"/>
+      <c r="C57" s="37">
         <v>6.97</v>
       </c>
-      <c r="D57" s="37">
+      <c r="D57" s="38">
         <v>-39.42</v>
       </c>
-      <c r="E57" s="37">
+      <c r="E57" s="38">
         <v>-28.02</v>
       </c>
-      <c r="F57" s="37">
+      <c r="F57" s="38">
         <v>-3.04</v>
       </c>
-      <c r="G57" s="32"/>
-      <c r="H57" s="37">
+      <c r="G57" s="33"/>
+      <c r="H57" s="38">
         <v>-7.99</v>
       </c>
-      <c r="I57" s="36">
+      <c r="I57" s="37">
         <v>1.62</v>
       </c>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-      <c r="N57" s="32"/>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="32"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="33"/>
+      <c r="N57" s="33"/>
+      <c r="O57" s="33"/>
+      <c r="P57" s="33"/>
+      <c r="Q57" s="33"/>
+      <c r="R57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
+      <c r="A58" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="B59" s="37">
         <v>0.61</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="37">
         <v>0.44</v>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="37">
         <v>0.45</v>
       </c>
-      <c r="E59" s="36">
+      <c r="E59" s="37">
         <v>0.54</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="37">
         <v>0.52</v>
       </c>
-      <c r="G59" s="36">
+      <c r="G59" s="37">
         <v>0.5</v>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="37">
         <v>0.57</v>
       </c>
-      <c r="I59" s="36">
+      <c r="I59" s="37">
         <v>0.61</v>
       </c>
-      <c r="J59" s="36">
+      <c r="J59" s="37">
         <v>0.76</v>
       </c>
-      <c r="K59" s="36">
+      <c r="K59" s="37">
         <v>0.7</v>
       </c>
-      <c r="L59" s="36">
+      <c r="L59" s="37">
         <v>0.72</v>
       </c>
-      <c r="M59" s="36">
+      <c r="M59" s="37">
         <v>0.62</v>
       </c>
-      <c r="N59" s="32"/>
-      <c r="O59" s="32"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="32"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>386</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="B60" s="37">
         <v>0.51</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="37">
         <v>0.49</v>
       </c>
-      <c r="D60" s="36">
+      <c r="D60" s="37">
         <v>0.51</v>
       </c>
-      <c r="E60" s="36">
+      <c r="E60" s="37">
         <v>0.55</v>
       </c>
-      <c r="F60" s="36">
+      <c r="F60" s="37">
         <v>0.59</v>
       </c>
-      <c r="G60" s="36">
+      <c r="G60" s="37">
         <v>0.63</v>
       </c>
-      <c r="H60" s="36">
+      <c r="H60" s="37">
         <v>0.67</v>
       </c>
-      <c r="I60" s="36">
+      <c r="I60" s="37">
         <v>0.68</v>
       </c>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="32"/>
-      <c r="O60" s="32"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>387</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="B62" s="36">
+      <c r="A62" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="B62" s="37">
         <v>9.2</v>
       </c>
-      <c r="C62" s="36">
+      <c r="C62" s="37">
         <v>6.63</v>
       </c>
-      <c r="D62" s="36">
+      <c r="D62" s="37">
         <v>5.9</v>
       </c>
-      <c r="E62" s="36">
+      <c r="E62" s="37">
         <v>8.98</v>
       </c>
-      <c r="F62" s="36">
+      <c r="F62" s="37">
         <v>10.75</v>
       </c>
-      <c r="G62" s="36">
+      <c r="G62" s="37">
         <v>17.68</v>
       </c>
-      <c r="H62" s="36">
+      <c r="H62" s="37">
         <v>9.08</v>
       </c>
-      <c r="I62" s="36">
+      <c r="I62" s="37">
         <v>8.31</v>
       </c>
-      <c r="J62" s="36">
+      <c r="J62" s="37">
         <v>10.24</v>
       </c>
-      <c r="K62" s="36">
+      <c r="K62" s="37">
         <v>9.48</v>
       </c>
-      <c r="L62" s="36">
+      <c r="L62" s="37">
         <v>9.81</v>
       </c>
-      <c r="M62" s="36">
+      <c r="M62" s="37">
         <v>8.35</v>
       </c>
-      <c r="N62" s="32"/>
-      <c r="O62" s="32"/>
-      <c r="P62" s="32"/>
-      <c r="Q62" s="32"/>
-      <c r="R62" s="32"/>
+      <c r="N62" s="33"/>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33"/>
+      <c r="Q62" s="33"/>
+      <c r="R62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
-        <v>389</v>
-      </c>
-      <c r="B63" s="36">
+      <c r="A63" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="B63" s="37">
         <v>8.02</v>
       </c>
-      <c r="C63" s="36">
+      <c r="C63" s="37">
         <v>10.09</v>
       </c>
-      <c r="D63" s="36">
+      <c r="D63" s="37">
         <v>10.89</v>
       </c>
-      <c r="E63" s="36">
+      <c r="E63" s="37">
         <v>11.83</v>
       </c>
-      <c r="F63" s="36">
+      <c r="F63" s="37">
         <v>12.04</v>
       </c>
-      <c r="G63" s="36">
+      <c r="G63" s="37">
         <v>11.53</v>
       </c>
-      <c r="H63" s="36">
+      <c r="H63" s="37">
         <v>9.4</v>
       </c>
-      <c r="I63" s="36">
+      <c r="I63" s="37">
         <v>9.25</v>
       </c>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
-      <c r="M63" s="32"/>
-      <c r="N63" s="32"/>
-      <c r="O63" s="32"/>
-      <c r="P63" s="32"/>
-      <c r="Q63" s="32"/>
-      <c r="R63" s="32"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>390</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>391</v>
-      </c>
-      <c r="B65" s="36">
+      <c r="A65" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="B65" s="37">
         <v>13.03</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="37">
         <v>9.75</v>
       </c>
-      <c r="D65" s="36">
+      <c r="D65" s="37">
         <v>9.93</v>
       </c>
-      <c r="E65" s="36">
+      <c r="E65" s="37">
         <v>11.96</v>
       </c>
-      <c r="F65" s="36">
+      <c r="F65" s="37">
         <v>11.61</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="36">
+      <c r="G65" s="33"/>
+      <c r="H65" s="37">
         <v>22.55</v>
       </c>
-      <c r="I65" s="36">
+      <c r="I65" s="37">
         <v>13.92</v>
       </c>
-      <c r="J65" s="36">
+      <c r="J65" s="37">
         <v>16.8</v>
       </c>
-      <c r="K65" s="36">
+      <c r="K65" s="37">
         <v>14.99</v>
       </c>
-      <c r="L65" s="36">
+      <c r="L65" s="37">
         <v>15.47</v>
       </c>
-      <c r="M65" s="36">
+      <c r="M65" s="37">
         <v>19.1</v>
       </c>
-      <c r="N65" s="32"/>
-      <c r="O65" s="32"/>
-      <c r="P65" s="32"/>
-      <c r="Q65" s="32"/>
-      <c r="R65" s="32"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="33"/>
+      <c r="R65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="B66" s="36">
+      <c r="A66" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="B66" s="37">
         <v>11.26</v>
       </c>
-      <c r="C66" s="36">
+      <c r="C66" s="37">
         <v>13.75</v>
       </c>
-      <c r="D66" s="36">
+      <c r="D66" s="37">
         <v>16.55</v>
       </c>
-      <c r="E66" s="36">
+      <c r="E66" s="37">
         <v>17.89</v>
       </c>
-      <c r="F66" s="36">
+      <c r="F66" s="37">
         <v>19.31</v>
       </c>
-      <c r="G66" s="36">
+      <c r="G66" s="37">
         <v>20.04</v>
       </c>
-      <c r="H66" s="36">
+      <c r="H66" s="37">
         <v>16.2</v>
       </c>
-      <c r="I66" s="36">
+      <c r="I66" s="37">
         <v>15.86</v>
       </c>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
-      <c r="M66" s="32"/>
-      <c r="N66" s="32"/>
-      <c r="O66" s="32"/>
-      <c r="P66" s="32"/>
-      <c r="Q66" s="32"/>
-      <c r="R66" s="32"/>
+      <c r="J66" s="33"/>
+      <c r="K66" s="33"/>
+      <c r="L66" s="33"/>
+      <c r="M66" s="33"/>
+      <c r="N66" s="33"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="33"/>
+      <c r="R66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>393</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
+      <c r="A67" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="B68" s="36">
+      <c r="A68" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B68" s="37">
         <v>15.64</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="37">
         <v>11.72</v>
       </c>
-      <c r="D68" s="36">
+      <c r="D68" s="37">
         <v>12.45</v>
       </c>
-      <c r="E68" s="36">
+      <c r="E68" s="37">
         <v>15.81</v>
       </c>
-      <c r="F68" s="36">
+      <c r="F68" s="37">
         <v>14.46</v>
       </c>
-      <c r="G68" s="32"/>
-      <c r="H68" s="36">
+      <c r="G68" s="33"/>
+      <c r="H68" s="37">
         <v>52.9</v>
       </c>
-      <c r="I68" s="36">
+      <c r="I68" s="37">
         <v>20.71</v>
       </c>
-      <c r="J68" s="36">
+      <c r="J68" s="37">
         <v>23.91</v>
       </c>
-      <c r="K68" s="36">
+      <c r="K68" s="37">
         <v>19.65</v>
       </c>
-      <c r="L68" s="36">
+      <c r="L68" s="37">
         <v>20.53</v>
       </c>
-      <c r="M68" s="36">
+      <c r="M68" s="37">
         <v>29.57</v>
       </c>
-      <c r="N68" s="32"/>
-      <c r="O68" s="32"/>
-      <c r="P68" s="32"/>
-      <c r="Q68" s="32"/>
-      <c r="R68" s="32"/>
+      <c r="N68" s="33"/>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="33"/>
+      <c r="R68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="B69" s="36">
+      <c r="A69" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="B69" s="37">
         <v>13.98</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="37">
         <v>18.63</v>
       </c>
-      <c r="D69" s="36">
+      <c r="D69" s="37">
         <v>25.27</v>
       </c>
-      <c r="E69" s="36">
+      <c r="E69" s="37">
         <v>29.09</v>
       </c>
-      <c r="F69" s="36">
+      <c r="F69" s="37">
         <v>32.23</v>
       </c>
-      <c r="G69" s="36">
+      <c r="G69" s="37">
         <v>33.65</v>
       </c>
-      <c r="H69" s="36">
+      <c r="H69" s="37">
         <v>23.55</v>
       </c>
-      <c r="I69" s="36">
+      <c r="I69" s="37">
         <v>22.23</v>
       </c>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
-      <c r="N69" s="32"/>
-      <c r="O69" s="32"/>
-      <c r="P69" s="32"/>
-      <c r="Q69" s="32"/>
-      <c r="R69" s="32"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
+      <c r="N69" s="33"/>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="33"/>
+      <c r="R69" s="33"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
